--- a/edim-ai-blueprint/docs/EDIM_권한승인정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_권한승인정의서.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문서보안등급" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'권한매트릭스'!$A$1:$J$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'권한매트릭스'!$A$1:$J$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4738,22 +4738,22 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>M-15-1</t>
+          <t>M-14-11</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>ERP</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>Company Info.</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>다국어 리소스 관리 (KO·EN·JA·ZH)</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -4766,14 +4766,14 @@
           <t>●</t>
         </is>
       </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>●</t>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J82" s="6" t="inlineStr"/>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>M-15-2</t>
+          <t>M-15-1</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>승인함</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>승인 요청·처리·이력</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>M-15-3</t>
+          <t>M-15-2</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>일정·To-do</t>
+          <t>승인함</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Schedule·To-do·Done</t>
+          <t>승인 요청·처리·이력</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>M-15-4</t>
+          <t>M-15-3</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>일정·To-do</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>알림 목록·공지</t>
+          <t>Schedule·To-do·Done</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>M-15-5</t>
+          <t>M-15-4</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -4932,12 +4932,12 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>업무 소통</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Project 중심 대화 (SNS)</t>
+          <t>알림 목록·공지</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>M-15-6</t>
+          <t>M-15-5</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>업무 소통</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Hierarchy·자료 통합 검색</t>
+          <t>Project 중심 대화 (SNS)</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>M-15-7</t>
+          <t>M-15-6</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>개인 설정</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>색상·언어·판넬 화면 조정</t>
+          <t>Hierarchy·자료 통합 검색</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>M-15-8</t>
+          <t>M-15-7</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Project Folder</t>
+          <t>개인 설정</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>산출물 탐색 (DWG·Price·Data·BOM)</t>
+          <t>색상·언어·판넬 화면 조정</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>M-15-9</t>
+          <t>M-15-8</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>이력 조회</t>
+          <t>Project Folder</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>생성·편집·삭제·승인 History</t>
+          <t>산출물 탐색 (DWG·Price·Data·BOM)</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -5134,14 +5134,14 @@
           <t>●</t>
         </is>
       </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I90" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>●</t>
         </is>
       </c>
       <c r="J90" s="6" t="inlineStr"/>
@@ -5152,22 +5152,22 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>M-16-1</t>
+          <t>M-15-9</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Mobile App</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>이력 조회</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>QR 정보 열람 (도면·서류·Project·업무)</t>
+          <t>생성·편집·삭제·승인 History</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -5180,14 +5180,14 @@
           <t>●</t>
         </is>
       </c>
-      <c r="H91" s="7" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>●</t>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J91" s="6" t="inlineStr"/>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>M-16-2</t>
+          <t>M-16-1</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>승인</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>업무 승인</t>
+          <t>QR 정보 열람 (도면·서류·Project·업무)</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -5226,14 +5226,14 @@
           <t>●</t>
         </is>
       </c>
-      <c r="H92" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I92" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>●</t>
         </is>
       </c>
       <c r="J92" s="6" t="inlineStr"/>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>M-16-3</t>
+          <t>M-16-2</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>소통</t>
+          <t>승인</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>Project 중심 대화·History</t>
+          <t>업무 승인</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -5272,14 +5272,14 @@
           <t>●</t>
         </is>
       </c>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>●</t>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J93" s="6" t="inlineStr"/>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>M-16-4</t>
+          <t>M-16-3</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>자재</t>
+          <t>소통</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>자재 입출고</t>
+          <t>Project 중심 대화·History</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -5313,26 +5313,22 @@
           <t>●</t>
         </is>
       </c>
-      <c r="G94" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H94" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J94" s="6" t="inlineStr">
-        <is>
-          <t>부서 제한: 자재</t>
-        </is>
-      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
@@ -5340,7 +5336,7 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>M-16-5</t>
+          <t>M-16-4</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -5350,12 +5346,12 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>검수</t>
+          <t>자재</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>자재·완성품·설치완료 검수</t>
+          <t>자재 입출고</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -5380,7 +5376,7 @@
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>부서 제한: QC</t>
+          <t>부서 제한: 자재</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5386,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>M-16-6</t>
+          <t>M-16-5</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
@@ -5400,12 +5396,12 @@
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>유지보수</t>
+          <t>검수</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Client 유지보수 접수·처리</t>
+          <t>자재·완성품·설치완료 검수</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -5430,7 +5426,7 @@
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>부서 제한: CS</t>
+          <t>부서 제한: QC</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5436,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>M-16-7</t>
+          <t>M-16-6</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -5450,12 +5446,12 @@
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>유지보수</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>공지·알림 수신</t>
+          <t>Client 유지보수 접수·처리</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -5463,22 +5459,26 @@
           <t>●</t>
         </is>
       </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="J97" s="6" t="inlineStr"/>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>부서 제한: CS</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
@@ -5486,52 +5486,98 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
+          <t>M-16-7</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>공지·알림 수신</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
           <t>M-16-8</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>Mobile App</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>증강현실 View</t>
         </is>
       </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="G98" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H98" s="9" t="inlineStr">
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J98" s="6" t="inlineStr">
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
         <is>
           <t>현장 모바일 사용자</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J98"/>
+  <autoFilter ref="A1:J99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
